--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260930.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260930.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>138,255</t>
+          <t>137,905</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.63%</t>
+          <t>26.49%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.20%</t>
+          <t>8.15%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>100,190</t>
+          <t>100,090</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.49%</t>
+          <t>7.51%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.28%</t>
+          <t>7.35%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>121,425</t>
+          <t>121,325</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>5.02%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>59,910</t>
+          <t>59,610</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.23%</t>
+          <t>4.36%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>18,383</t>
+          <t>18,283</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.47%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
@@ -792,51 +792,51 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>19,825</t>
+          <t>45,245</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>45,245</t>
+          <t>19,725</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>77,245</t>
+          <t>76,895</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>20,345</t>
+          <t>20,245</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>21,408</t>
+          <t>21,308</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,56 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>634,161</t>
+          <t>662,835</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.36%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>12,723,200</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>RDI_USD</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>295,497</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
